--- a/data/raw/附件2 市主城区 10 区域分时段充电车次.xlsx
+++ b/data/raw/附件2 市主城区 10 区域分时段充电车次.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="工作日分时段充电车次数据" sheetId="1" r:id="rId1"/>
@@ -1081,7 +1081,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Y12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="2" t="s">
@@ -1967,7 +1967,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Y12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="2" t="s">
